--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104459_W1.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104459_W1.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2702</v>
+        <v>6.1617</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0252</v>
+        <v>3.6131</v>
       </c>
       <c r="F2" t="n">
-        <v>2.245</v>
+        <v>2.5486</v>
       </c>
       <c r="G2" t="n">
-        <v>3.346</v>
+        <v>3.3381</v>
       </c>
       <c r="H2" t="n">
-        <v>1.091</v>
+        <v>1.0859</v>
       </c>
       <c r="I2" t="n">
-        <v>2.255</v>
+        <v>2.2522</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6977</v>
+        <v>2.6772</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1704</v>
+        <v>1.1581</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5273</v>
+        <v>1.519</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6483</v>
+        <v>0.6609</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8223</v>
+        <v>0.0708</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7652</v>
+        <v>-0.1535</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0572</v>
+        <v>0.2243</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1936</v>
+        <v>3.6807</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2815</v>
+        <v>3.9548</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.274</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1805</v>
+        <v>1.1812</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2209</v>
+        <v>0.2157</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9596</v>
+        <v>0.9655</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2189</v>
+        <v>2.1978</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0248</v>
+        <v>1.0062</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1941</v>
+        <v>1.1916</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0384</v>
+        <v>-1.0166</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1473</v>
+        <v>0.6377</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4688</v>
+        <v>0.2413</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6161</v>
+        <v>0.3964</v>
       </c>
       <c r="V3" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7886</v>
+        <v>2.5588</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5881</v>
+        <v>-0.5967</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3767</v>
+        <v>3.1555</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0169</v>
+        <v>3.0113</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.07779999999999999</v>
+        <v>-0.0857</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0947</v>
+        <v>3.097</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7982</v>
+        <v>1.7752</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6274</v>
+        <v>-0.6452</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4256</v>
+        <v>2.4204</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2187</v>
+        <v>1.2361</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5496</v>
+        <v>0.5595</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5468</v>
+        <v>0.3183</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1179</v>
+        <v>-0.0955</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.4138</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. SULEJMANOVIC</t>
+          <t>A. DIAZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3304</v>
+        <v>1.6565</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3396</v>
+        <v>1.6817</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9908</v>
+        <v>-0.0252</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7356</v>
+        <v>1.5464</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7995</v>
+        <v>0.2637</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0639</v>
+        <v>1.2827</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8019</v>
+        <v>2.5486</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6899</v>
+        <v>0.7239</v>
       </c>
       <c r="L5" t="n">
-        <v>0.112</v>
+        <v>1.8246</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0663</v>
+        <v>-1.0022</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1096</v>
+        <v>-0.4603</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1759</v>
+        <v>-0.5419</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.4952</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6609</v>
+        <v>0.18</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8721</v>
+        <v>0.3412</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7887999999999999</v>
+        <v>-0.1612</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. TILLIE</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7843</v>
+        <v>1.4513</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1841</v>
+        <v>0.7317</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9684</v>
+        <v>0.7197</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1076</v>
+        <v>-0.617</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4083</v>
+        <v>-0.1239</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3008</v>
+        <v>-0.4931</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.293</v>
+        <v>-0.1146</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2051</v>
+        <v>0.6378</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4981</v>
+        <v>-0.7524</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4006</v>
+        <v>-0.5023</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2033</v>
+        <v>-0.7617</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1973</v>
+        <v>0.2593</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9036</v>
+        <v>0.2276</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2431</v>
+        <v>0.1438</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6605</v>
+        <v>0.0838</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DIAZ</t>
+          <t>T. PEREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4826</v>
+        <v>1.0586</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8122</v>
+        <v>0.1548</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3296</v>
+        <v>0.9038</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5333</v>
+        <v>-1.0242</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2538</v>
+        <v>0.0634</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2795</v>
+        <v>-1.0875</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5558</v>
+        <v>-0.881</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.6238</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8285</v>
+        <v>-1.5048</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0225</v>
+        <v>-0.1432</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4735</v>
+        <v>-0.5604</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.549</v>
+        <v>0.4173</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0154</v>
+        <v>0.1707</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4567</v>
+        <v>-0.0536</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4413</v>
+        <v>0.2243</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1607</v>
+        <v>0.7739</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. PEREZ</t>
+          <t>E. SULEJMANOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4353</v>
+        <v>0.849</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4581</v>
+        <v>0.0886</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9772</v>
+        <v>0.7605</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0185</v>
+        <v>1.732</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0664</v>
+        <v>1.7898</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0849</v>
+        <v>-0.0578</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8645</v>
+        <v>1.7869</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6336000000000001</v>
+        <v>1.6752</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4981</v>
+        <v>0.1117</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.154</v>
+        <v>-0.0549</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5672</v>
+        <v>0.1146</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4132</v>
+        <v>-0.1695</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5483</v>
+        <v>1.1869</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2299</v>
+        <v>0.6478</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3185</v>
+        <v>0.5391</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7712</v>
+        <v>-0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3214</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>K. TILLIE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8465</v>
+        <v>0.6374</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2691</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5774</v>
+        <v>1.5492</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6246</v>
+        <v>0.1054</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1314</v>
+        <v>1.4074</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4931</v>
+        <v>-1.302</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1083</v>
+        <v>-0.3122</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6407</v>
+        <v>1.1926</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.749</v>
+        <v>-1.5048</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5162</v>
+        <v>0.4176</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7721</v>
+        <v>0.2148</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2559</v>
+        <v>0.2028</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q9" t="n">
+        <v>-1.1382</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.9105</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.7597</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.5386</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.2211</v>
+      </c>
+      <c r="V9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.1342</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.3702</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.3297</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.0405</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.7071</v>
-      </c>
       <c r="W9" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5593</v>
+        <v>0.3012</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6197</v>
+        <v>0.1492</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0603</v>
+        <v>0.152</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3911</v>
+        <v>1.3888</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3895</v>
+        <v>-0.396</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7806</v>
+        <v>1.7847</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9429</v>
+        <v>0.9278</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3259</v>
+        <v>-0.3382</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4483</v>
+        <v>0.4609</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4197</v>
+        <v>1.1613</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8771</v>
+        <v>0.4294</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5426</v>
+        <v>0.7319</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9267</v>
+        <v>-0.349</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6408</v>
+        <v>-3.0979</v>
       </c>
       <c r="F11" t="n">
-        <v>2.7141</v>
+        <v>2.7489</v>
       </c>
       <c r="G11" t="n">
-        <v>2.398</v>
+        <v>2.3891</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9048</v>
+        <v>1.8961</v>
       </c>
       <c r="I11" t="n">
         <v>0.4931</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8001</v>
+        <v>1.7687</v>
       </c>
       <c r="K11" t="n">
-        <v>1.5443</v>
+        <v>1.5233</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2558</v>
+        <v>0.2453</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5979</v>
+        <v>0.6204</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3605</v>
+        <v>0.3727</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7349</v>
+        <v>-0.1462</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9043</v>
+        <v>-0.3139</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1693</v>
+        <v>0.1677</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2711</v>
+        <v>-0.3617</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.579</v>
+        <v>-1.8848</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3079</v>
+        <v>1.5231</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9677</v>
+        <v>1.9616</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2266</v>
+        <v>1.2182</v>
       </c>
       <c r="I12" t="n">
-        <v>0.741</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4526</v>
+        <v>1.4282</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0075</v>
+        <v>0.989</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5151</v>
+        <v>0.5335</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9212</v>
+        <v>-0.0046</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7652</v>
+        <v>-0.0351</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1561</v>
+        <v>0.0305</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8639</v>
+        <v>-1.8634</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6893</v>
+        <v>-3.1574</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.6978</v>
+        <v>-4.374</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0085</v>
+        <v>1.2167</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.2297</v>
+        <v>-2.2358</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.1529</v>
+        <v>-1.1572</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.0769</v>
+        <v>-1.0786</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.0999</v>
+        <v>-2.1231</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1989</v>
+        <v>-1.2141</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.901</v>
+        <v>-0.909</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1299</v>
+        <v>-0.1127</v>
       </c>
       <c r="N13" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.643</v>
+        <v>-0.1021</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3297</v>
+        <v>0.0253</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3133</v>
+        <v>-0.1275</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.8037</v>
+        <v>14.48710000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8844000000000016</v>
+        <v>-0.4913000000000007</v>
       </c>
       <c r="F14" t="n">
-        <v>14.6882</v>
+        <v>14.9788</v>
       </c>
       <c r="G14" t="n">
-        <v>12.8039</v>
+        <v>12.7769</v>
       </c>
       <c r="H14" t="n">
-        <v>6.2197</v>
+        <v>6.1774</v>
       </c>
       <c r="I14" t="n">
-        <v>6.5839</v>
+        <v>6.599600000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>11.9024</v>
+        <v>11.6795</v>
       </c>
       <c r="K14" t="n">
-        <v>7.491399999999999</v>
+        <v>7.332400000000002</v>
       </c>
       <c r="L14" t="n">
-        <v>4.411</v>
+        <v>4.346900000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9015999999999998</v>
+        <v>1.0975</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2716</v>
+        <v>-1.1554</v>
       </c>
       <c r="O14" t="n">
-        <v>2.1729</v>
+        <v>2.2529</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.2682</v>
+        <v>-2.2762</v>
       </c>
       <c r="Q14" t="n">
-        <v>-19.2809</v>
+        <v>-19.3486</v>
       </c>
       <c r="R14" t="n">
-        <v>17.0126</v>
+        <v>17.0726</v>
       </c>
       <c r="S14" t="n">
-        <v>3.750400000000001</v>
+        <v>4.4601</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9980999999999999</v>
+        <v>1.7158</v>
       </c>
       <c r="U14" t="n">
-        <v>2.7522</v>
+        <v>2.7442</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4820999999999999</v>
+        <v>-0.4733000000000003</v>
       </c>
       <c r="W14" t="n">
-        <v>5.4958</v>
+        <v>5.4624</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.977799999999998</v>
+        <v>-5.935499999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.65</v>
+        <v>3.3592</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6493</v>
+        <v>3.4472</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0007</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2761</v>
+        <v>2.2854</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1081</v>
+        <v>2.1108</v>
       </c>
       <c r="I15" t="n">
-        <v>0.168</v>
+        <v>0.1746</v>
       </c>
       <c r="J15" t="n">
-        <v>4.0768</v>
+        <v>4.0612</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7707</v>
+        <v>2.7579</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3061</v>
+        <v>1.3033</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8007</v>
+        <v>-1.7758</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5573</v>
+        <v>0.2543</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3852</v>
+        <v>0.2086</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1721</v>
+        <v>0.0457</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5168</v>
+        <v>3.1869</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7501</v>
+        <v>2.0779</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7668</v>
+        <v>1.109</v>
       </c>
       <c r="G16" t="n">
-        <v>3.2669</v>
+        <v>3.2702</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4068</v>
+        <v>0.4132</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8601</v>
+        <v>2.8569</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6494</v>
+        <v>3.6274</v>
       </c>
       <c r="K16" t="n">
-        <v>0.928</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>2.7214</v>
+        <v>2.7106</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3825</v>
+        <v>-0.3573</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5212</v>
+        <v>-0.5036</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5893</v>
+        <v>-0.9255</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7652</v>
+        <v>-0.4114</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8242</v>
+        <v>-0.5141</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9276</v>
+        <v>1.5683</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3695</v>
+        <v>0.8263</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5581</v>
+        <v>0.742</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8324</v>
+        <v>-0.8182</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2007</v>
+        <v>-0.1929</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6317</v>
+        <v>-0.6254</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1403</v>
+        <v>-0.1464</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2149</v>
+        <v>-0.2208</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6921</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8544</v>
+        <v>-0.2265</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9043</v>
+        <v>-0.4324</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0499</v>
+        <v>0.2058</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. LAZAREVIC</t>
+          <t>D. HILLIARD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0417</v>
+        <v>0.3096</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.5058</v>
+        <v>-0.3571</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4641</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2335</v>
+        <v>-1.0505</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3694</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.136</v>
+        <v>-0.9732</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3232</v>
+        <v>0.1516</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3605</v>
+        <v>0.3685</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>-0.2169</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9103</v>
+        <v>-1.2022</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0089</v>
+        <v>-0.4458</v>
       </c>
       <c r="O18" t="n">
-        <v>0.09859999999999999</v>
+        <v>-0.7563</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4452</v>
+        <v>-0.5911</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0484</v>
+        <v>-0.4114</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4936</v>
+        <v>-0.1797</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1607</v>
+        <v>2.1789</v>
       </c>
       <c r="W18" t="n">
+        <v>2.1789</v>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-0.1607</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. HILLIARD</t>
+          <t>S. LAZAREVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.334</v>
+        <v>-0.6403</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6615</v>
+        <v>-1.7573</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3275</v>
+        <v>1.117</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0359</v>
+        <v>-1.2259</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0735</v>
+        <v>-1.3645</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9623</v>
+        <v>0.1387</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1867</v>
+        <v>-0.3355</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3841</v>
+        <v>-0.3727</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1974</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2225</v>
+        <v>-0.8904</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4576</v>
+        <v>-0.9918</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7649</v>
+        <v>0.1014</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2567</v>
+        <v>-0.1672</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7652</v>
+        <v>-0.2837</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4915</v>
+        <v>0.1165</v>
       </c>
       <c r="V19" t="n">
-        <v>2.1853</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.753</v>
+        <v>-1.1349</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0968</v>
+        <v>-1.4563</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3439</v>
+        <v>0.3214</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6576</v>
+        <v>-1.6563</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8499</v>
+        <v>-0.8474</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8077</v>
+        <v>-0.8089</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1222</v>
+        <v>-0.1143</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4509</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4386</v>
+        <v>0.0858</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0124</v>
+        <v>-0.0196</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2267</v>
+        <v>-1.9539</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.3469</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5367</v>
+        <v>-1.607</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7357</v>
+        <v>-1.7257</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7144</v>
+        <v>-1.7064</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0213</v>
+        <v>-0.0193</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3854</v>
+        <v>-0.3904</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4227</v>
+        <v>-0.4277</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3503</v>
+        <v>-1.3353</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2917</v>
+        <v>-1.2788</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3076</v>
+        <v>-0.0476</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6261</v>
+        <v>-0.272</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3185</v>
+        <v>0.2243</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. FREY</t>
+          <t>M. NORMANTAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.231</v>
+        <v>-3.1038</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2484</v>
+        <v>-3.9701</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0174</v>
+        <v>0.8663</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9888</v>
+        <v>-3.5242</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2294</v>
+        <v>-0.3913</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2181</v>
+        <v>-3.1329</v>
       </c>
       <c r="J22" t="n">
-        <v>0.396</v>
+        <v>-2.1905</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2224</v>
+        <v>0.9308</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8264</v>
+        <v>-3.1213</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3848</v>
+        <v>-1.3337</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.993</v>
+        <v>-1.3221</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3918</v>
+        <v>-0.0116</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>2.722</v>
+        <v>2.5039</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3021</v>
+        <v>-0.8966</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5293</v>
+        <v>-0.5927</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2271</v>
+        <v>-0.3039</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8639</v>
+        <v>1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7712</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. NORMANTAS</t>
+          <t>H. FREY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7575</v>
+        <v>-3.7496</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5312</v>
+        <v>-3.9901</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.2404</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.5309</v>
+        <v>-0.9861</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4042</v>
+        <v>0.2325</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.1267</v>
+        <v>-1.2185</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.173</v>
+        <v>0.3753</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9351</v>
+        <v>1.2098</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.1081</v>
+        <v>-0.8345</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3579</v>
+        <v>-1.3613</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3393</v>
+        <v>-0.9774</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0186</v>
+        <v>-0.384</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2268</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4952</v>
+        <v>2.7316</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5461</v>
+        <v>-0.2173</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1825</v>
+        <v>-0.1769</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3636</v>
+        <v>-0.0403</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0927</v>
+        <v>-1.8634</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>-0.7739</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1009</v>
+        <v>-5.1104</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2329</v>
+        <v>-4.2722</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8681</v>
+        <v>-0.8381999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.1456</v>
+        <v>-4.1485</v>
       </c>
       <c r="H24" t="n">
         <v>-2.6796</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4661</v>
+        <v>-1.4689</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.9609</v>
+        <v>-2.9872</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.9852</v>
+        <v>-2.0037</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.9756</v>
+        <v>-0.9835</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1848</v>
+        <v>-1.1613</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6944</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2571</v>
+        <v>-0.2559</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0484</v>
+        <v>0.0468</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.4532</v>
+        <v>-5.7319</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.4903</v>
+        <v>-5.1801</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9629</v>
+        <v>-0.5517</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.1864</v>
+        <v>-3.1971</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.6724</v>
+        <v>-1.6743</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.5141</v>
+        <v>-1.5228</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.6921</v>
+        <v>-1.7211</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.1989</v>
+        <v>-1.2141</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4932</v>
+        <v>-0.5071</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.4944</v>
+        <v>-1.4759</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R25" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7431</v>
+        <v>-0.0128</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5565</v>
+        <v>-0.2023</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1866</v>
+        <v>0.1895</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.6429</v>
+        <v>-0.6311</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-13.8036</v>
+        <v>-13.0008</v>
       </c>
       <c r="E26" t="n">
-        <v>-14.688</v>
+        <v>-14.9787</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8845</v>
+        <v>1.978</v>
       </c>
       <c r="G26" t="n">
-        <v>-12.8038</v>
+        <v>-12.7769</v>
       </c>
       <c r="H26" t="n">
-        <v>-6.219799999999999</v>
+        <v>-6.1772</v>
       </c>
       <c r="I26" t="n">
-        <v>-6.583900000000001</v>
+        <v>-6.5997</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.9013999999999993</v>
+        <v>-1.097599999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>1.2717</v>
+        <v>1.1552</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.173</v>
+        <v>-2.2529</v>
       </c>
       <c r="M26" t="n">
-        <v>-11.9025</v>
+        <v>-11.6794</v>
       </c>
       <c r="N26" t="n">
-        <v>-7.491599999999998</v>
+        <v>-7.332600000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>-4.410900000000001</v>
+        <v>-4.3468</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2684</v>
+        <v>2.2764</v>
       </c>
       <c r="Q26" t="n">
-        <v>-17.0125</v>
+        <v>-17.0725</v>
       </c>
       <c r="R26" t="n">
-        <v>19.2809</v>
+        <v>19.3488</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.7504</v>
+        <v>-2.973199999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.7522</v>
+        <v>-2.7443</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9980999999999999</v>
+        <v>-0.2289999999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>0.4821000000000001</v>
+        <v>0.4733000000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>5.9778</v>
+        <v>5.935499999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.4958</v>
+        <v>-5.4624</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104459_W1.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104459_W1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-5.935499999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.6311</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104459_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-5.4624</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
